--- a/public/template/Contractor_Timesheet_PY26.xlsx
+++ b/public/template/Contractor_Timesheet_PY26.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>PAY PERIOD START DATE:</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>RSD</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -1701,6 +1704,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24" spans="17:17">
+      <c r="Q24" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="28" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -1815,7 +1823,7 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:J11" xr:uid="{FE72575B-4D31-461B-8B70-EF178FAB2AF4}">
-      <formula1>$Q$13:$Q$23</formula1>
+      <formula1>$Q$13:$Q$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{3BA8D67A-8029-407B-B7E9-B82C38C569CE}">
       <formula1>$S$13:$S$16</formula1>
